--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_arica_y_parinacota.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:50</t>
+    <t xml:space="preserve">2026-09-09 20:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_arica_y_parinacota.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:56</t>
+    <t xml:space="preserve">2026-09-18 10:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_arica_y_parinacota.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:46</t>
+    <t xml:space="preserve">2026-09-23 16:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_arica_y_parinacota.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2023_arica_y_parinacota.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 16:30</t>
+    <t xml:space="preserve">2026-10-05 06:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
